--- a/34th_Backgammon-championships_5a_output.xlsx
+++ b/34th_Backgammon-championships_5a_output.xlsx
@@ -1009,7 +1009,7 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
         <v>5</v>
@@ -1064,10 +1064,10 @@
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>7</v>
@@ -1079,7 +1079,7 @@
         <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -1137,7 +1137,7 @@
         <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
         <v>7</v>
@@ -1165,7 +1165,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
@@ -1183,28 +1183,28 @@
         <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L7" t="n">
         <v>9</v>
       </c>
       <c r="M7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N7" t="n">
         <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P7" t="n">
         <v>9</v>
       </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1223,7 +1223,7 @@
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -1455,7 +1455,7 @@
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
         <v>8</v>
